--- a/test-files/test-with-discrepancies.xlsx
+++ b/test-files/test-with-discrepancies.xlsx
@@ -397,7 +397,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F6"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,7 +438,7 @@
         <v>Capsule</v>
       </c>
       <c r="D2">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="E2" t="str">
         <v>medicaid</v>
@@ -447,10 +455,10 @@
         <v>10 mg</v>
       </c>
       <c r="C3" t="str">
-        <v>Tablet</v>
+        <v>Capsule</v>
       </c>
       <c r="D3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E3" t="str">
         <v>medicaid</v>
@@ -464,10 +472,10 @@
         <v>Metformin</v>
       </c>
       <c r="B4" t="str">
-        <v>500 mg</v>
+        <v>1000 mg</v>
       </c>
       <c r="C4" t="str">
-        <v>Capsule</v>
+        <v>Tablet (ER)</v>
       </c>
       <c r="D4">
         <v>0.15</v>
@@ -484,16 +492,16 @@
         <v>Simvastatin</v>
       </c>
       <c r="B5" t="str">
-        <v>40 mg</v>
+        <v>20 mg</v>
       </c>
       <c r="C5" t="str">
         <v>Tablet</v>
       </c>
       <c r="D5">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="E5" t="str">
-        <v>medicare</v>
+        <v>medicaid</v>
       </c>
       <c r="F5">
         <v>30</v>
@@ -501,87 +509,27 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Omeprazole</v>
+        <v>Unknown Drug XYZ</v>
       </c>
       <c r="B6" t="str">
-        <v>20 mg</v>
+        <v>50 mg</v>
       </c>
       <c r="C6" t="str">
-        <v>Capsule (DR)</v>
+        <v>Tablet</v>
       </c>
       <c r="D6">
-        <v>0.3</v>
+        <v>25</v>
       </c>
       <c r="E6" t="str">
         <v>medicaid</v>
       </c>
       <c r="F6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Loratadine</v>
-      </c>
-      <c r="B7" t="str">
-        <v>10 mg</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Syrup</v>
-      </c>
-      <c r="D7">
-        <v>0.3</v>
-      </c>
-      <c r="E7" t="str">
-        <v>medicare</v>
-      </c>
-      <c r="F7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Unknown Drug XYZ</v>
-      </c>
-      <c r="B8" t="str">
-        <v>100 mg</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Tablet</v>
-      </c>
-      <c r="D8">
         <v>15</v>
-      </c>
-      <c r="E8" t="str">
-        <v>medicaid</v>
-      </c>
-      <c r="F8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Prednisone</v>
-      </c>
-      <c r="B9" t="str">
-        <v>10 mg</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Tablet</v>
-      </c>
-      <c r="D9">
-        <v>0.4</v>
-      </c>
-      <c r="E9" t="str">
-        <v>medicare</v>
-      </c>
-      <c r="F9">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
   </ignoredErrors>
 </worksheet>
 </file>